--- a/data/user_input.xlsx
+++ b/data/user_input.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20430" windowHeight="8160"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -58,19 +47,19 @@
     <t>USA</t>
   </si>
   <si>
-    <t>Diversified Real Estate</t>
-  </si>
-  <si>
-    <t>Barings Real Estate</t>
-  </si>
-  <si>
-    <t>Charlotte, NC</t>
-  </si>
-  <si>
-    <t>27B</t>
-  </si>
-  <si>
-    <t>https://www.barings.com</t>
+    <t>CenterSquare Investment Management</t>
+  </si>
+  <si>
+    <t>Blue Bell, PA</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>https://centersquare.com</t>
+  </si>
+  <si>
+    <t>Listed REIT Securities</t>
   </si>
 </sst>
 </file>
@@ -391,8 +380,9 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
     <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
     <col min="5" max="5" width="34.28515625" customWidth="1"/>
     <col min="6" max="6" width="31" customWidth="1"/>
   </cols>
@@ -417,24 +407,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/user_input.xlsx
+++ b/data/user_input.xlsx
@@ -14,17 +14,28 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>Company Name</t>
   </si>
@@ -44,35 +55,116 @@
     <t>REIT Focus / Asset Type</t>
   </si>
   <si>
+    <t>Realty Income Corporation</t>
+  </si>
+  <si>
     <t>USA</t>
   </si>
   <si>
-    <t>CenterSquare Investment Management</t>
-  </si>
-  <si>
-    <t>Blue Bell, PA</t>
+    <t>San Diego, CA</t>
+  </si>
+  <si>
+    <t>20B</t>
+  </si>
+  <si>
+    <t>https://www.realtyincome.com</t>
+  </si>
+  <si>
+    <t>Net Lease REIT</t>
+  </si>
+  <si>
+    <t>STORE Capital</t>
+  </si>
+  <si>
+    <t>Scottsdale, AZ</t>
   </si>
   <si>
     <t>12B</t>
   </si>
   <si>
-    <t>https://centersquare.com</t>
-  </si>
-  <si>
-    <t>Listed REIT Securities</t>
+    <t>https://www.storecapital.com</t>
+  </si>
+  <si>
+    <t>Physicians Realty Trust</t>
+  </si>
+  <si>
+    <t>Milwaukee, WI</t>
+  </si>
+  <si>
+    <t>5B</t>
+  </si>
+  <si>
+    <t>https://www.docreit.com</t>
+  </si>
+  <si>
+    <t>Healthcare REIT</t>
+  </si>
+  <si>
+    <t>Eastdil Secured</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>10B</t>
+  </si>
+  <si>
+    <t>https://www.eastdilsecured.com</t>
+  </si>
+  <si>
+    <t>Real Estate Capital</t>
+  </si>
+  <si>
+    <t>Mack-Cali Realty</t>
+  </si>
+  <si>
+    <t>Jersey City, NJ</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>https://www.mack-cali.com</t>
+  </si>
+  <si>
+    <t>Office/Multifamily REIT</t>
+  </si>
+  <si>
+    <t>COMPANY_LINKEDIN_URL_HEADER</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/realty-income-corporation</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/store-capital</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/healthpeak/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/eastdil-secured/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/mack-cali-realty-corporation/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF374151"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -95,8 +187,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -377,17 +473,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="27.28515625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
     <col min="5" max="5" width="34.28515625" customWidth="1"/>
     <col min="6" max="6" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -406,13 +501,16 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -425,12 +523,112 @@
       </c>
       <c r="F2" t="s">
         <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/data/user_input.xlsx
+++ b/data/user_input.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20430" windowHeight="8160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>Company Name</t>
   </si>
@@ -55,97 +55,97 @@
     <t>REIT Focus / Asset Type</t>
   </si>
   <si>
-    <t>Realty Income Corporation</t>
-  </si>
-  <si>
     <t>USA</t>
   </si>
   <si>
-    <t>San Diego, CA</t>
-  </si>
-  <si>
-    <t>20B</t>
-  </si>
-  <si>
-    <t>https://www.realtyincome.com</t>
-  </si>
-  <si>
-    <t>Net Lease REIT</t>
-  </si>
-  <si>
-    <t>STORE Capital</t>
-  </si>
-  <si>
-    <t>Scottsdale, AZ</t>
-  </si>
-  <si>
-    <t>12B</t>
-  </si>
-  <si>
-    <t>https://www.storecapital.com</t>
-  </si>
-  <si>
-    <t>Physicians Realty Trust</t>
-  </si>
-  <si>
-    <t>Milwaukee, WI</t>
-  </si>
-  <si>
-    <t>5B</t>
-  </si>
-  <si>
-    <t>https://www.docreit.com</t>
-  </si>
-  <si>
-    <t>Healthcare REIT</t>
-  </si>
-  <si>
-    <t>Eastdil Secured</t>
-  </si>
-  <si>
-    <t>New York, NY</t>
-  </si>
-  <si>
-    <t>10B</t>
-  </si>
-  <si>
-    <t>https://www.eastdilsecured.com</t>
-  </si>
-  <si>
-    <t>Real Estate Capital</t>
-  </si>
-  <si>
-    <t>Mack-Cali Realty</t>
-  </si>
-  <si>
-    <t>Jersey City, NJ</t>
+    <t>1B</t>
+  </si>
+  <si>
+    <t>Cottonwood Communities</t>
+  </si>
+  <si>
+    <t>Salt Lake City, UT</t>
+  </si>
+  <si>
+    <t>https://www.cottonwoodcommunities.com</t>
+  </si>
+  <si>
+    <t>Multifamily REIT</t>
+  </si>
+  <si>
+    <t>Passco Companies</t>
+  </si>
+  <si>
+    <t>Irvine, CA</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>https://www.passco.com</t>
+  </si>
+  <si>
+    <t>Multifamily/Commercial REIT</t>
+  </si>
+  <si>
+    <t>Inland Private Capital</t>
+  </si>
+  <si>
+    <t>Oak Brook, IL</t>
+  </si>
+  <si>
+    <t>8B</t>
+  </si>
+  <si>
+    <t>https://www.inlandprivatecapital.com</t>
+  </si>
+  <si>
+    <t>Diversified Real Estate</t>
+  </si>
+  <si>
+    <t>Grubb Properties</t>
+  </si>
+  <si>
+    <t>Charlotte, NC</t>
+  </si>
+  <si>
+    <t>https://www.grubbproperties.com</t>
+  </si>
+  <si>
+    <t>Industrial Logistics Properties Trust</t>
+  </si>
+  <si>
+    <t>Newton, MA</t>
   </si>
   <si>
     <t>4B</t>
   </si>
   <si>
-    <t>https://www.mack-cali.com</t>
-  </si>
-  <si>
-    <t>Office/Multifamily REIT</t>
+    <t>https://www.ilptreit.com</t>
+  </si>
+  <si>
+    <t>Industrial REIT</t>
   </si>
   <si>
     <t>COMPANY_LINKEDIN_URL_HEADER</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/company/realty-income-corporation</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/company/store-capital</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/company/healthpeak/</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/company/eastdil-secured/</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/company/mack-cali-realty-corporation/</t>
+    <t>Invalid Website URL</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/industrial-logistics-properties-trust</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/grubb-properties</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/inland-real-estate-investment-corp/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/passco/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/cottonwood-residential/</t>
   </si>
 </sst>
 </file>
@@ -161,10 +161,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF374151"/>
-      <name val="Courier New"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -184,17 +186,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -473,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -482,7 +483,7 @@
     <col min="6" max="6" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -502,38 +503,41 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -541,83 +545,83 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
         <v>19</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>25</v>
       </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>29</v>
       </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
+      <c r="G6" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -627,8 +631,10 @@
     <hyperlink ref="E4" r:id="rId3"/>
     <hyperlink ref="E5" r:id="rId4"/>
     <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="G6" r:id="rId6"/>
+    <hyperlink ref="G5" r:id="rId7"/>
+    <hyperlink ref="G2" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>